--- a/XD_JIG/XD12/XD12_PWM_Rev_0/Docs/XDIC(PWM)_TEST_241107.xlsx
+++ b/XD_JIG/XD12/XD12_PWM_Rev_0/Docs/XDIC(PWM)_TEST_241107.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD12_JIG\XD12_PWM\Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD12\XD12_PWM_Rev_0\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AAC708B-86CF-4150-A12D-B4AA717C1FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B700265-9EE2-477C-AD49-F7A9C0E8E9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="4095" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1579,6 +1579,51 @@
     <xf numFmtId="176" fontId="11" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1587,51 +1632,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2596,35 +2596,35 @@
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="2:10" ht="17.25" thickBot="1">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="47"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="32"/>
     </row>
     <row r="3" spans="2:10" ht="17.25" thickBot="1">
       <c r="I3" s="1"/>
     </row>
     <row r="4" spans="2:10" ht="19.05" customHeight="1" thickBot="1">
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="44"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="35"/>
       <c r="G4" s="6"/>
-      <c r="H4" s="39" t="s">
+      <c r="H4" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="I4" s="40"/>
-      <c r="J4" s="41"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="38"/>
     </row>
     <row r="5" spans="2:10">
       <c r="B5" s="2" t="s">
@@ -2690,13 +2690,13 @@
       <c r="J7" s="12"/>
     </row>
     <row r="8" spans="2:10" ht="17.25" thickBot="1">
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="44"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="35"/>
       <c r="G8" s="6"/>
       <c r="H8" s="17" t="s">
         <v>5</v>
@@ -2747,11 +2747,11 @@
         <v>2</v>
       </c>
       <c r="G10" s="6"/>
-      <c r="H10" s="39" t="s">
+      <c r="H10" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="I10" s="40"/>
-      <c r="J10" s="41"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="38"/>
     </row>
     <row r="11" spans="2:10">
       <c r="B11" s="6"/>
@@ -2818,12 +2818,12 @@
       </c>
     </row>
     <row r="15" spans="2:10" ht="17.25" thickBot="1">
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="44"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="35"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
@@ -2840,16 +2840,16 @@
       <c r="D16" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="E16" s="30" t="s">
+      <c r="E16" s="45" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="33" t="s">
+      <c r="H16" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="I16" s="34"/>
-      <c r="J16" s="35"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="41"/>
     </row>
     <row r="17" spans="2:10">
       <c r="B17" s="20" t="s">
@@ -2861,7 +2861,7 @@
       <c r="D17" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E17" s="31"/>
+      <c r="E17" s="46"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="7" t="s">
@@ -2884,7 +2884,7 @@
       <c r="D18" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E18" s="31"/>
+      <c r="E18" s="46"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="22" t="s">
@@ -2907,7 +2907,7 @@
       <c r="D19" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="E19" s="32"/>
+      <c r="E19" s="47"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="10" t="s">
@@ -2928,7 +2928,7 @@
       <c r="D20" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="E20" s="36" t="s">
+      <c r="E20" s="42" t="s">
         <v>26</v>
       </c>
       <c r="F20" s="6"/>
@@ -2953,7 +2953,7 @@
       <c r="D21" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E21" s="37"/>
+      <c r="E21" s="43"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -2970,14 +2970,14 @@
       <c r="D22" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E22" s="37"/>
+      <c r="E22" s="43"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="33" t="s">
+      <c r="H22" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="I22" s="34"/>
-      <c r="J22" s="35"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="41"/>
     </row>
     <row r="23" spans="2:10" ht="17.25" thickBot="1">
       <c r="B23" s="24" t="s">
@@ -2989,7 +2989,7 @@
       <c r="D23" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="E23" s="38"/>
+      <c r="E23" s="44"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="7" t="s">
@@ -3047,36 +3047,36 @@
       <c r="J27" s="6"/>
     </row>
     <row r="28" spans="2:10" ht="17" customHeight="1" thickBot="1">
-      <c r="B28" s="45" t="s">
+      <c r="B28" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="C28" s="46"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="46"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="46"/>
-      <c r="I28" s="46"/>
-      <c r="J28" s="47"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="32"/>
     </row>
     <row r="29" spans="2:10" ht="17.25" thickBot="1">
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
     </row>
     <row r="30" spans="2:10" ht="17.25" thickBot="1">
-      <c r="B30" s="42" t="s">
+      <c r="B30" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="43"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="44"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="35"/>
       <c r="G30" s="6"/>
-      <c r="H30" s="39" t="s">
+      <c r="H30" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="I30" s="40"/>
-      <c r="J30" s="41"/>
+      <c r="I30" s="37"/>
+      <c r="J30" s="38"/>
     </row>
     <row r="31" spans="2:10">
       <c r="B31" s="2" t="s">
@@ -3143,13 +3143,13 @@
       <c r="J33" s="12"/>
     </row>
     <row r="34" spans="2:10" ht="17.25" thickBot="1">
-      <c r="B34" s="42" t="s">
+      <c r="B34" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="43"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="44"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="35"/>
       <c r="G34" s="6"/>
       <c r="H34" s="17" t="s">
         <v>5</v>
@@ -3201,11 +3201,11 @@
         <v>2</v>
       </c>
       <c r="G36" s="6"/>
-      <c r="H36" s="39" t="s">
+      <c r="H36" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="I36" s="40"/>
-      <c r="J36" s="41"/>
+      <c r="I36" s="37"/>
+      <c r="J36" s="38"/>
     </row>
     <row r="37" spans="2:10">
       <c r="B37" s="6"/>
@@ -3272,12 +3272,12 @@
       </c>
     </row>
     <row r="41" spans="2:10" ht="17.25" thickBot="1">
-      <c r="B41" s="42" t="s">
+      <c r="B41" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="43"/>
-      <c r="D41" s="43"/>
-      <c r="E41" s="44"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="35"/>
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
@@ -3294,16 +3294,16 @@
       <c r="D42" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="E42" s="30" t="s">
+      <c r="E42" s="45" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>
-      <c r="H42" s="33" t="s">
+      <c r="H42" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="I42" s="34"/>
-      <c r="J42" s="35"/>
+      <c r="I42" s="40"/>
+      <c r="J42" s="41"/>
     </row>
     <row r="43" spans="2:10">
       <c r="B43" s="20" t="s">
@@ -3315,7 +3315,7 @@
       <c r="D43" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E43" s="31"/>
+      <c r="E43" s="46"/>
       <c r="F43" s="6"/>
       <c r="G43" s="6"/>
       <c r="H43" s="7" t="s">
@@ -3338,7 +3338,7 @@
       <c r="D44" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E44" s="31"/>
+      <c r="E44" s="46"/>
       <c r="F44" s="6"/>
       <c r="G44" s="6"/>
       <c r="H44" s="22" t="s">
@@ -3361,7 +3361,7 @@
       <c r="D45" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="E45" s="32"/>
+      <c r="E45" s="47"/>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="10" t="s">
@@ -3382,7 +3382,7 @@
       <c r="D46" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="E46" s="36" t="s">
+      <c r="E46" s="42" t="s">
         <v>26</v>
       </c>
       <c r="F46" s="6"/>
@@ -3407,7 +3407,7 @@
       <c r="D47" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E47" s="37"/>
+      <c r="E47" s="43"/>
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
@@ -3424,14 +3424,14 @@
       <c r="D48" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E48" s="37"/>
+      <c r="E48" s="43"/>
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
-      <c r="H48" s="33" t="s">
+      <c r="H48" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="I48" s="34"/>
-      <c r="J48" s="35"/>
+      <c r="I48" s="40"/>
+      <c r="J48" s="41"/>
     </row>
     <row r="49" spans="2:10" ht="17.25" thickBot="1">
       <c r="B49" s="24" t="s">
@@ -3443,7 +3443,7 @@
       <c r="D49" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="E49" s="38"/>
+      <c r="E49" s="44"/>
       <c r="F49" s="6"/>
       <c r="G49" s="6"/>
       <c r="H49" s="7" t="s">
@@ -3495,6 +3495,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="E42:E45"/>
+    <mergeCell ref="H42:J42"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="H48:J48"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="B41:E41"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B28:J28"/>
     <mergeCell ref="B30:F30"/>
@@ -3509,12 +3515,6 @@
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="E16:E19"/>
     <mergeCell ref="B15:E15"/>
-    <mergeCell ref="E42:E45"/>
-    <mergeCell ref="H42:J42"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="H48:J48"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="B41:E41"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3562,27 +3562,27 @@
       </c>
     </row>
     <row r="3" spans="2:18" ht="17.25" thickBot="1">
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="44"/>
-      <c r="H3" s="42" t="s">
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="35"/>
+      <c r="H3" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="44"/>
-      <c r="N3" s="42" t="s">
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="35"/>
+      <c r="N3" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="O3" s="43"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="44"/>
+      <c r="O3" s="34"/>
+      <c r="P3" s="34"/>
+      <c r="Q3" s="34"/>
+      <c r="R3" s="35"/>
     </row>
     <row r="4" spans="2:18">
       <c r="B4" s="2" t="s">
@@ -3685,27 +3685,27 @@
     </row>
     <row r="6" spans="2:18" ht="17.25" thickBot="1"/>
     <row r="7" spans="2:18" ht="17.25" thickBot="1">
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="44"/>
-      <c r="H7" s="42" t="s">
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="35"/>
+      <c r="H7" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="43"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="43"/>
-      <c r="L7" s="44"/>
-      <c r="N7" s="42" t="s">
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="35"/>
+      <c r="N7" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="O7" s="43"/>
-      <c r="P7" s="43"/>
-      <c r="Q7" s="43"/>
-      <c r="R7" s="44"/>
+      <c r="O7" s="34"/>
+      <c r="P7" s="34"/>
+      <c r="Q7" s="34"/>
+      <c r="R7" s="35"/>
     </row>
     <row r="8" spans="2:18">
       <c r="B8" s="2" t="s">
@@ -3842,27 +3842,27 @@
       </c>
     </row>
     <row r="12" spans="2:18" ht="17.25" thickBot="1">
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="44"/>
-      <c r="H12" s="42" t="s">
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="35"/>
+      <c r="H12" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="I12" s="43"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="43"/>
-      <c r="L12" s="44"/>
-      <c r="N12" s="42" t="s">
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="35"/>
+      <c r="N12" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="O12" s="43"/>
-      <c r="P12" s="43"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="44"/>
+      <c r="O12" s="34"/>
+      <c r="P12" s="34"/>
+      <c r="Q12" s="34"/>
+      <c r="R12" s="35"/>
     </row>
     <row r="13" spans="2:18">
       <c r="B13" s="2" t="s">
@@ -3966,27 +3966,27 @@
     </row>
     <row r="15" spans="2:18" ht="17.25" thickBot="1"/>
     <row r="16" spans="2:18" ht="17.25" thickBot="1">
-      <c r="B16" s="42" t="s">
+      <c r="B16" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="44"/>
-      <c r="H16" s="42" t="s">
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="35"/>
+      <c r="H16" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="44"/>
-      <c r="N16" s="42" t="s">
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="35"/>
+      <c r="N16" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="O16" s="43"/>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="43"/>
-      <c r="R16" s="44"/>
+      <c r="O16" s="34"/>
+      <c r="P16" s="34"/>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="35"/>
     </row>
     <row r="17" spans="2:18">
       <c r="B17" s="2" t="s">
@@ -4090,18 +4090,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="H7:L7"/>
+    <mergeCell ref="N3:R3"/>
+    <mergeCell ref="N7:R7"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="H12:L12"/>
     <mergeCell ref="H16:L16"/>
     <mergeCell ref="N12:R12"/>
     <mergeCell ref="N16:R16"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="H7:L7"/>
-    <mergeCell ref="N3:R3"/>
-    <mergeCell ref="N7:R7"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
